--- a/config/role_frame.xlsx
+++ b/config/role_frame.xlsx
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>初期フレーム</t>
+          <t>初始帧</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>黄金の調査員</t>
+          <t>黄金调查员</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>S1フレーム</t>
+          <t>S1帧</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>S2フレーム</t>
+          <t>S2帧</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>S3フレーム</t>
+          <t>S3帧</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>S4フレーム</t>
+          <t>S4帧</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>S5フレーム</t>
+          <t>S5框架</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>S6フレーム</t>
+          <t>S6框架</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>S7フレーム</t>
+          <t>S7框架</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>S8フレーム</t>
+          <t>S8框架</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>S9フレーム</t>
+          <t>S9框架</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>S10フレーム</t>
+          <t>S10帧</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>雪の聖夜</t>
+          <t>雪之圣夜</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>クリスマス</t>
+          <t>圣诞节</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>謹賀新年(2026)</t>
+          <t>新年快乐（2026）</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
